--- a/data/ct_scoop/ct_scoop_links_2026-06-26.xlsx
+++ b/data/ct_scoop/ct_scoop_links_2026-06-26.xlsx
@@ -1,130 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t>heading</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>link</t>
-  </si>
-  <si>
-    <t>FARMINGTON SCOOP: Construction now underway at former Barnes &amp; Noble for 4 new tenants!</t>
-  </si>
-  <si>
-    <t>MANCHESTER SCOOP: The Angry Egg returns to Manchester</t>
-  </si>
-  <si>
-    <t>BERLIN SCOOP: Imperial Buffet closes amid tax permit suspension</t>
-  </si>
-  <si>
-    <t>EAST WINDSOR SCOOP: Molly's Sweet Spot to open on June</t>
-  </si>
-  <si>
-    <t>LISBON SCOOP: Ulta Beauty to close on July 11th</t>
-  </si>
-  <si>
-    <t>MULTI-TOWN SCOOP: Hooters closes final 3 Massachusetts locations</t>
-  </si>
-  <si>
-    <t>MANCHESTER SCOOP: Ground broken for new 'Silk City Commons' development at old Parkade site!</t>
-  </si>
-  <si>
-    <t>TRUMBULL SCOOP: Apple permanently closes at Trumbull Mall</t>
-  </si>
-  <si>
-    <t>HELL'S KITCHEN SCOOP: Casting call for 3 fun events for Hell's Kitchen!</t>
-  </si>
-  <si>
-    <t>7 BREW SCOOP: 7 Brew eyeing locations in Norwich, Waterford, &amp; Groton!</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/farmington-scoop-construction-now-underway-at-former-barnes-noble-for-4-new-tenants</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-the-angry-egg-returns-to-manchester</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/berlin-scoop-imperial-buffet-closes-amid-tax-permit-suspension</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/east-windsor-scoop-mollys-sweet-spot-to-open-on-june</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/lisbon-scoop-ulta-beauty-to-close-on-july-11th</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-mass-posts/multi-town-scoop-hooters-closes-final-3-massachusetts-locations</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-ground-broken-for-new-silk-city-commons-development-at-old-parkade-site</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/trumbull-scoop-apple-permanently-closes-at-trumbull-mall</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/hells-kitchen-scoop-casting-call-for-3-fun-events-for-hells-kitchen</t>
-  </si>
-  <si>
-    <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/norwich-waterford-scoop-7-brew-eyeing-new-locations</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -132,43 +45,86 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -456,144 +412,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FARMINGTON SCOOP: Construction now underway at former Barnes &amp; Noble for 4 new tenants!</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/farmington-scoop-construction-now-underway-at-former-barnes-noble-for-4-new-tenants</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MANCHESTER SCOOP: The Angry Egg returns to Manchester</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-the-angry-egg-returns-to-manchester</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BERLIN SCOOP: Imperial Buffet closes amid tax permit suspension</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/berlin-scoop-imperial-buffet-closes-amid-tax-permit-suspension</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EAST WINDSOR SCOOP: Molly's Sweet Spot to open on June</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/east-windsor-scoop-mollys-sweet-spot-to-open-on-june</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LISBON SCOOP: Ulta Beauty to close on July 11th</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/lisbon-scoop-ulta-beauty-to-close-on-july-11th</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MULTI-TOWN SCOOP: Hooters closes final 3 Massachusetts locations</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-mass-posts/multi-town-scoop-hooters-closes-final-3-massachusetts-locations</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MANCHESTER SCOOP: Ground broken for new 'Silk City Commons' development at old Parkade site!</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>46197</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-ground-broken-for-new-silk-city-commons-development-at-old-parkade-site</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TRUMBULL SCOOP: Apple permanently closes at Trumbull Mall</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>46197</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/trumbull-scoop-apple-permanently-closes-at-trumbull-mall</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HELL'S KITCHEN SCOOP: Casting call for 3 fun events for Hell's Kitchen!</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
         <v>46197</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/hells-kitchen-scoop-casting-call-for-3-fun-events-for-hells-kitchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7 BREW SCOOP: 7 Brew eyeing locations in Norwich, Waterford, &amp; Groton!</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>46197</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>22</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/norwich-waterford-scoop-7-brew-eyeing-new-locations</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C3" r:id="rId2"/>
-    <hyperlink ref="C4" r:id="rId3"/>
-    <hyperlink ref="C5" r:id="rId4"/>
-    <hyperlink ref="C6" r:id="rId5"/>
-    <hyperlink ref="C7" r:id="rId6"/>
-    <hyperlink ref="C8" r:id="rId7"/>
-    <hyperlink ref="C9" r:id="rId8"/>
-    <hyperlink ref="C10" r:id="rId9"/>
-    <hyperlink ref="C11" r:id="rId10"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>